--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -599,18 +599,18 @@
           <t>L6: suspicious token(s): 6wer (letter/digit mix) :: to be still fur- 6wer in the old form, will be done away with to a greater</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: only â€” namely</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: onlyâ€”namelj</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L18: isolated marker/symbol line :: 144</t>
@@ -618,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: &gt;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,16 +658,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a claim,â€” tha</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a claim,â€”tha</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -677,7 +669,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: /</t>
+          <t>L70: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -713,16 +705,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”that is, how far may the case be resist</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”that is, how far may the case he resisted by affidavits, and</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -732,7 +716,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 1</t>
+          <t>L72: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -768,11 +752,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: spoken of as being â€œso wide in its</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -783,7 +763,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: N</t>
+          <t>L103: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -824,7 +804,11 @@
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: N</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -961,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1044,7 +1028,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
